--- a/backend/data_wizard/import_templates/vulnerabilities_template.xlsx
+++ b/backend/data_wizard/import_templates/vulnerabilities_template.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.0625" defaultRowHeight="13.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19.95" customWidth="1" style="3" min="1" max="3"/>
@@ -472,6 +472,7 @@
     <col width="76.34" customWidth="1" style="3" min="5" max="5"/>
     <col width="39.92" customWidth="1" style="3" min="6" max="6"/>
     <col width="19.5" customWidth="1" style="3" min="7" max="7"/>
+    <col width="60" customWidth="1" style="3" min="8" max="8"/>
     <col width="10.87" customWidth="1" style="3" min="1014" max="1024"/>
   </cols>
   <sheetData>
@@ -511,6 +512,11 @@
           <t>filtering_labels</t>
         </is>
       </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>observation</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="32.05" customHeight="1" s="4">
       <c r="A2" s="3" t="inlineStr">
@@ -549,6 +555,11 @@
 code-injection</t>
         </is>
       </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Input sanitization fix scheduled for the next release.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="32.05" customHeight="1" s="4">
       <c r="A3" s="3" t="inlineStr">
@@ -587,6 +598,7 @@
           <t>wifi</t>
         </is>
       </c>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="1048572" ht="12.8" customHeight="1" s="4"/>
     <row r="1048573" ht="12.8" customHeight="1" s="4"/>
